--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136402433</v>
       </c>
       <c r="B2" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136392821</v>
       </c>
       <c r="B16" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136396104</v>
       </c>
       <c r="B17" t="n">
-        <v>91872</v>
+        <v>91881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136386035</v>
       </c>
       <c r="B18" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>136376836</v>
       </c>
       <c r="B19" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136380121</v>
       </c>
       <c r="B20" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>136381954</v>
       </c>
       <c r="B21" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>136384925</v>
       </c>
       <c r="B22" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>136386039</v>
       </c>
       <c r="B23" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>136386054</v>
       </c>
       <c r="B24" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>136386055</v>
       </c>
       <c r="B25" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>136386073</v>
       </c>
       <c r="B26" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>136386075</v>
       </c>
       <c r="B27" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>136386082</v>
       </c>
       <c r="B28" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>136386084</v>
       </c>
       <c r="B29" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136386090</v>
       </c>
       <c r="B30" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136392727</v>
       </c>
       <c r="B31" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136392735</v>
       </c>
       <c r="B32" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136392741</v>
       </c>
       <c r="B33" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>136392756</v>
       </c>
       <c r="B34" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136392771</v>
       </c>
       <c r="B35" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136392794</v>
       </c>
       <c r="B36" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136392800</v>
       </c>
       <c r="B37" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136392803</v>
       </c>
       <c r="B38" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136392811</v>
       </c>
       <c r="B39" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136392812</v>
       </c>
       <c r="B40" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>136392813</v>
       </c>
       <c r="B41" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>136392823</v>
       </c>
       <c r="B42" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>136392828</v>
       </c>
       <c r="B43" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>136393469</v>
       </c>
       <c r="B44" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>136396101</v>
       </c>
       <c r="B45" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>136396122</v>
       </c>
       <c r="B46" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>136396125</v>
       </c>
       <c r="B47" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>136396129</v>
       </c>
       <c r="B48" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>136396130</v>
       </c>
       <c r="B49" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>136396135</v>
       </c>
       <c r="B50" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>136396148</v>
       </c>
       <c r="B51" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>136396149</v>
       </c>
       <c r="B52" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>136396152</v>
       </c>
       <c r="B53" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>136396154</v>
       </c>
       <c r="B54" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136396155</v>
       </c>
       <c r="B55" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>136396156</v>
       </c>
       <c r="B56" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>136402412</v>
       </c>
       <c r="B57" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>136402421</v>
       </c>
       <c r="B58" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>136402428</v>
       </c>
       <c r="B59" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136402429</v>
       </c>
       <c r="B60" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136402434</v>
       </c>
       <c r="B61" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>136402436</v>
       </c>
       <c r="B62" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>136402438</v>
       </c>
       <c r="B63" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>136402439</v>
       </c>
       <c r="B64" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136402441</v>
       </c>
       <c r="B65" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>136402442</v>
       </c>
       <c r="B66" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>136405164</v>
       </c>
       <c r="B67" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136402408</v>
       </c>
       <c r="B68" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>136386041</v>
       </c>
       <c r="B69" t="n">
-        <v>89314</v>
+        <v>89316</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>136386050</v>
       </c>
       <c r="B70" t="n">
-        <v>89314</v>
+        <v>89316</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>136392816</v>
       </c>
       <c r="B71" t="n">
-        <v>93072</v>
+        <v>93075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>136402409</v>
       </c>
       <c r="B72" t="n">
-        <v>93072</v>
+        <v>93075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>136382713</v>
       </c>
       <c r="B75" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136392764</v>
       </c>
       <c r="B76" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>136396142</v>
       </c>
       <c r="B77" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>136396143</v>
       </c>
       <c r="B78" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>136402426</v>
       </c>
       <c r="B79" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>136402422</v>
       </c>
       <c r="B80" t="n">
-        <v>91461</v>
+        <v>91463</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>136392786</v>
       </c>
       <c r="B81" t="n">
-        <v>93384</v>
+        <v>93387</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>136392810</v>
       </c>
       <c r="B316" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>136392787</v>
       </c>
       <c r="B317" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>136396123</v>
       </c>
       <c r="B318" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>136392749</v>
       </c>
       <c r="B319" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136402433</v>
       </c>
       <c r="B2" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136392821</v>
       </c>
       <c r="B16" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136396104</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136386035</v>
       </c>
       <c r="B18" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>136376836</v>
       </c>
       <c r="B19" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136380121</v>
       </c>
       <c r="B20" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>136381954</v>
       </c>
       <c r="B21" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>136384925</v>
       </c>
       <c r="B22" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>136386039</v>
       </c>
       <c r="B23" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>136386054</v>
       </c>
       <c r="B24" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>136386055</v>
       </c>
       <c r="B25" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>136386073</v>
       </c>
       <c r="B26" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>136386075</v>
       </c>
       <c r="B27" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>136386082</v>
       </c>
       <c r="B28" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>136386084</v>
       </c>
       <c r="B29" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136386090</v>
       </c>
       <c r="B30" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136392727</v>
       </c>
       <c r="B31" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136392735</v>
       </c>
       <c r="B32" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136392741</v>
       </c>
       <c r="B33" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>136392756</v>
       </c>
       <c r="B34" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136392771</v>
       </c>
       <c r="B35" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136392794</v>
       </c>
       <c r="B36" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136392800</v>
       </c>
       <c r="B37" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136392803</v>
       </c>
       <c r="B38" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136392811</v>
       </c>
       <c r="B39" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136392812</v>
       </c>
       <c r="B40" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>136392813</v>
       </c>
       <c r="B41" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>136392823</v>
       </c>
       <c r="B42" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>136392828</v>
       </c>
       <c r="B43" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>136393469</v>
       </c>
       <c r="B44" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>136396101</v>
       </c>
       <c r="B45" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>136396122</v>
       </c>
       <c r="B46" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>136396125</v>
       </c>
       <c r="B47" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>136396129</v>
       </c>
       <c r="B48" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>136396130</v>
       </c>
       <c r="B49" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>136396135</v>
       </c>
       <c r="B50" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>136396148</v>
       </c>
       <c r="B51" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>136396149</v>
       </c>
       <c r="B52" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>136396152</v>
       </c>
       <c r="B53" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>136396154</v>
       </c>
       <c r="B54" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136396155</v>
       </c>
       <c r="B55" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>136396156</v>
       </c>
       <c r="B56" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>136402412</v>
       </c>
       <c r="B57" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>136402421</v>
       </c>
       <c r="B58" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>136402428</v>
       </c>
       <c r="B59" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136402429</v>
       </c>
       <c r="B60" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136402434</v>
       </c>
       <c r="B61" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>136402436</v>
       </c>
       <c r="B62" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>136402438</v>
       </c>
       <c r="B63" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>136402439</v>
       </c>
       <c r="B64" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136402441</v>
       </c>
       <c r="B65" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>136402442</v>
       </c>
       <c r="B66" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>136405164</v>
       </c>
       <c r="B67" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136402408</v>
       </c>
       <c r="B68" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>136392816</v>
       </c>
       <c r="B71" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>136402409</v>
       </c>
       <c r="B72" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>136382713</v>
       </c>
       <c r="B75" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136392764</v>
       </c>
       <c r="B76" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>136396142</v>
       </c>
       <c r="B77" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>136396143</v>
       </c>
       <c r="B78" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>136402426</v>
       </c>
       <c r="B79" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>136392786</v>
       </c>
       <c r="B81" t="n">
-        <v>93387</v>
+        <v>93388</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>136392810</v>
       </c>
       <c r="B316" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>136392787</v>
       </c>
       <c r="B317" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>136396123</v>
       </c>
       <c r="B318" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>136392749</v>
       </c>
       <c r="B319" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136402433</v>
       </c>
       <c r="B2" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136392725</v>
       </c>
       <c r="B3" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136379790</v>
       </c>
       <c r="B4" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136384395</v>
       </c>
       <c r="B5" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136392737</v>
       </c>
       <c r="B6" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>136392768</v>
       </c>
       <c r="B7" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136392775</v>
       </c>
       <c r="B8" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>136392792</v>
       </c>
       <c r="B9" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136392793</v>
       </c>
       <c r="B10" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>136396115</v>
       </c>
       <c r="B11" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>136396133</v>
       </c>
       <c r="B12" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>136402411</v>
       </c>
       <c r="B13" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>136402419</v>
       </c>
       <c r="B14" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136402423</v>
       </c>
       <c r="B15" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136392821</v>
       </c>
       <c r="B16" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136396104</v>
       </c>
       <c r="B17" t="n">
-        <v>91882</v>
+        <v>91887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136386035</v>
       </c>
       <c r="B18" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>136376836</v>
       </c>
       <c r="B19" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136380121</v>
       </c>
       <c r="B20" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>136381954</v>
       </c>
       <c r="B21" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>136384925</v>
       </c>
       <c r="B22" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>136386039</v>
       </c>
       <c r="B23" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>136386054</v>
       </c>
       <c r="B24" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>136386055</v>
       </c>
       <c r="B25" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>136386073</v>
       </c>
       <c r="B26" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>136386075</v>
       </c>
       <c r="B27" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>136386082</v>
       </c>
       <c r="B28" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>136386084</v>
       </c>
       <c r="B29" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136386090</v>
       </c>
       <c r="B30" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136392727</v>
       </c>
       <c r="B31" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136392735</v>
       </c>
       <c r="B32" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136392741</v>
       </c>
       <c r="B33" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>136392756</v>
       </c>
       <c r="B34" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136392771</v>
       </c>
       <c r="B35" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136392794</v>
       </c>
       <c r="B36" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136392800</v>
       </c>
       <c r="B37" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136392803</v>
       </c>
       <c r="B38" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136392811</v>
       </c>
       <c r="B39" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136392812</v>
       </c>
       <c r="B40" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>136392813</v>
       </c>
       <c r="B41" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>136392823</v>
       </c>
       <c r="B42" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>136392828</v>
       </c>
       <c r="B43" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>136393469</v>
       </c>
       <c r="B44" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>136396101</v>
       </c>
       <c r="B45" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>136396122</v>
       </c>
       <c r="B46" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>136396125</v>
       </c>
       <c r="B47" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>136396129</v>
       </c>
       <c r="B48" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>136396130</v>
       </c>
       <c r="B49" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>136396135</v>
       </c>
       <c r="B50" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>136396148</v>
       </c>
       <c r="B51" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>136396149</v>
       </c>
       <c r="B52" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>136396152</v>
       </c>
       <c r="B53" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>136396154</v>
       </c>
       <c r="B54" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136396155</v>
       </c>
       <c r="B55" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>136396156</v>
       </c>
       <c r="B56" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>136402412</v>
       </c>
       <c r="B57" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>136402421</v>
       </c>
       <c r="B58" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>136402428</v>
       </c>
       <c r="B59" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136402429</v>
       </c>
       <c r="B60" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136402434</v>
       </c>
       <c r="B61" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>136402436</v>
       </c>
       <c r="B62" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>136402438</v>
       </c>
       <c r="B63" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>136402439</v>
       </c>
       <c r="B64" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136402441</v>
       </c>
       <c r="B65" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>136402442</v>
       </c>
       <c r="B66" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>136405164</v>
       </c>
       <c r="B67" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136402408</v>
       </c>
       <c r="B68" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>136386041</v>
       </c>
       <c r="B69" t="n">
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>136386050</v>
       </c>
       <c r="B70" t="n">
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>136392816</v>
       </c>
       <c r="B71" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>136402409</v>
       </c>
       <c r="B72" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>136382713</v>
       </c>
       <c r="B75" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136392764</v>
       </c>
       <c r="B76" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>136396142</v>
       </c>
       <c r="B77" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>136396143</v>
       </c>
       <c r="B78" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>136402426</v>
       </c>
       <c r="B79" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>136402422</v>
       </c>
       <c r="B80" t="n">
-        <v>91463</v>
+        <v>91465</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>136392786</v>
       </c>
       <c r="B81" t="n">
-        <v>93388</v>
+        <v>93393</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>136376332</v>
       </c>
       <c r="B108" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>136376665</v>
       </c>
       <c r="B109" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>136377035</v>
       </c>
       <c r="B110" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>136382303</v>
       </c>
       <c r="B111" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>136386037</v>
       </c>
       <c r="B112" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>136386040</v>
       </c>
       <c r="B113" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>136386051</v>
       </c>
       <c r="B114" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>136386056</v>
       </c>
       <c r="B115" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136386057</v>
       </c>
       <c r="B116" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136386058</v>
       </c>
       <c r="B117" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136386059</v>
       </c>
       <c r="B118" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136386060</v>
       </c>
       <c r="B119" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136386061</v>
       </c>
       <c r="B120" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>136386064</v>
       </c>
       <c r="B121" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>136386066</v>
       </c>
       <c r="B122" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>136386067</v>
       </c>
       <c r="B123" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>136386070</v>
       </c>
       <c r="B124" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>136386071</v>
       </c>
       <c r="B125" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>136386072</v>
       </c>
       <c r="B126" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>136386087</v>
       </c>
       <c r="B127" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>136386089</v>
       </c>
       <c r="B128" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>136392705</v>
       </c>
       <c r="B129" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>136392738</v>
       </c>
       <c r="B130" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>136392752</v>
       </c>
       <c r="B131" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>136392755</v>
       </c>
       <c r="B132" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>136392757</v>
       </c>
       <c r="B133" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>136392769</v>
       </c>
       <c r="B134" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>136392772</v>
       </c>
       <c r="B135" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>136392773</v>
       </c>
       <c r="B136" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>136392779</v>
       </c>
       <c r="B137" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>136392780</v>
       </c>
       <c r="B138" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>136392790</v>
       </c>
       <c r="B139" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>136392795</v>
       </c>
       <c r="B140" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>136392796</v>
       </c>
       <c r="B141" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>136392805</v>
       </c>
       <c r="B142" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>136392818</v>
       </c>
       <c r="B143" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>136392820</v>
       </c>
       <c r="B144" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>136392827</v>
       </c>
       <c r="B145" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>136392829</v>
       </c>
       <c r="B146" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>136393453</v>
       </c>
       <c r="B147" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>136393455</v>
       </c>
       <c r="B148" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>136393456</v>
       </c>
       <c r="B149" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>136393458</v>
       </c>
       <c r="B150" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>136393459</v>
       </c>
       <c r="B151" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>136393460</v>
       </c>
       <c r="B152" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>136393461</v>
       </c>
       <c r="B153" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>136393462</v>
       </c>
       <c r="B154" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>136393463</v>
       </c>
       <c r="B155" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>136393464</v>
       </c>
       <c r="B156" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>136393465</v>
       </c>
       <c r="B157" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>136393468</v>
       </c>
       <c r="B158" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>136393472</v>
       </c>
       <c r="B159" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>136393475</v>
       </c>
       <c r="B160" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>136393482</v>
       </c>
       <c r="B161" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>136393483</v>
       </c>
       <c r="B162" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>136393484</v>
       </c>
       <c r="B163" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>136393485</v>
       </c>
       <c r="B164" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>136393489</v>
       </c>
       <c r="B165" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>136393490</v>
       </c>
       <c r="B166" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>136393492</v>
       </c>
       <c r="B167" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>136393493</v>
       </c>
       <c r="B168" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>136393496</v>
       </c>
       <c r="B169" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>136393497</v>
       </c>
       <c r="B170" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>136393498</v>
       </c>
       <c r="B171" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>136393500</v>
       </c>
       <c r="B172" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>136393503</v>
       </c>
       <c r="B173" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>136393505</v>
       </c>
       <c r="B174" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>136393506</v>
       </c>
       <c r="B175" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>136393509</v>
       </c>
       <c r="B176" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>136393512</v>
       </c>
       <c r="B177" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>136393515</v>
       </c>
       <c r="B178" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>136393518</v>
       </c>
       <c r="B179" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>136393519</v>
       </c>
       <c r="B180" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>136393520</v>
       </c>
       <c r="B181" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>136393524</v>
       </c>
       <c r="B182" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>136393525</v>
       </c>
       <c r="B183" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>136393527</v>
       </c>
       <c r="B184" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>136396107</v>
       </c>
       <c r="B185" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>136396109</v>
       </c>
       <c r="B186" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>136396112</v>
       </c>
       <c r="B187" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>136396113</v>
       </c>
       <c r="B188" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>136396118</v>
       </c>
       <c r="B189" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>136396119</v>
       </c>
       <c r="B190" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>136396128</v>
       </c>
       <c r="B191" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>136396132</v>
       </c>
       <c r="B192" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>136396136</v>
       </c>
       <c r="B193" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>136396138</v>
       </c>
       <c r="B194" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>136396140</v>
       </c>
       <c r="B195" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>136396145</v>
       </c>
       <c r="B196" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>136396150</v>
       </c>
       <c r="B197" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>136396159</v>
       </c>
       <c r="B198" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>136402413</v>
       </c>
       <c r="B199" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>136402430</v>
       </c>
       <c r="B200" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>136386074</v>
       </c>
       <c r="B201" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>136392732</v>
       </c>
       <c r="B202" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>136392798</v>
       </c>
       <c r="B203" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>136383035</v>
       </c>
       <c r="B219" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>136386044</v>
       </c>
       <c r="B220" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>136386047</v>
       </c>
       <c r="B221" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>136386053</v>
       </c>
       <c r="B222" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>136386062</v>
       </c>
       <c r="B223" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>136386069</v>
       </c>
       <c r="B224" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>136386077</v>
       </c>
       <c r="B225" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>136392744</v>
       </c>
       <c r="B226" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>136392746</v>
       </c>
       <c r="B227" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>136393467</v>
       </c>
       <c r="B228" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>136393476</v>
       </c>
       <c r="B229" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>136393487</v>
       </c>
       <c r="B230" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>136393502</v>
       </c>
       <c r="B231" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>136393504</v>
       </c>
       <c r="B232" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>136393513</v>
       </c>
       <c r="B233" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>136393516</v>
       </c>
       <c r="B234" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>136393522</v>
       </c>
       <c r="B235" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>136396153</v>
       </c>
       <c r="B236" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>136402414</v>
       </c>
       <c r="B237" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>136402437</v>
       </c>
       <c r="B238" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>136386042</v>
       </c>
       <c r="B241" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>136386043</v>
       </c>
       <c r="B242" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>136386045</v>
       </c>
       <c r="B243" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>136386048</v>
       </c>
       <c r="B244" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>136386052</v>
       </c>
       <c r="B245" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>136386063</v>
       </c>
       <c r="B246" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>136386065</v>
       </c>
       <c r="B247" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>136386068</v>
       </c>
       <c r="B248" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>136386078</v>
       </c>
       <c r="B249" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>136386081</v>
       </c>
       <c r="B250" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>136386083</v>
       </c>
       <c r="B251" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>136392720</v>
       </c>
       <c r="B252" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>136392742</v>
       </c>
       <c r="B253" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>136392753</v>
       </c>
       <c r="B254" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>136392804</v>
       </c>
       <c r="B255" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>136393486</v>
       </c>
       <c r="B256" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>136393508</v>
       </c>
       <c r="B257" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>136393510</v>
       </c>
       <c r="B258" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>136396158</v>
       </c>
       <c r="B259" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>136402420</v>
       </c>
       <c r="B260" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>136386086</v>
       </c>
       <c r="B266" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>136392750</v>
       </c>
       <c r="B267" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>136392758</v>
       </c>
       <c r="B268" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>136392759</v>
       </c>
       <c r="B269" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>136392762</v>
       </c>
       <c r="B270" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>136392774</v>
       </c>
       <c r="B271" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>136392788</v>
       </c>
       <c r="B272" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>136392791</v>
       </c>
       <c r="B273" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>136392797</v>
       </c>
       <c r="B274" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>136392807</v>
       </c>
       <c r="B275" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>136392822</v>
       </c>
       <c r="B276" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>136396103</v>
       </c>
       <c r="B277" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>136386036</v>
       </c>
       <c r="B278" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>136386088</v>
       </c>
       <c r="B279" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>136392707</v>
       </c>
       <c r="B280" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>136392713</v>
       </c>
       <c r="B281" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>136392819</v>
       </c>
       <c r="B282" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>136392824</v>
       </c>
       <c r="B283" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>136392825</v>
       </c>
       <c r="B284" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>136393478</v>
       </c>
       <c r="B285" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>136376480</v>
       </c>
       <c r="B288" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>136376605</v>
       </c>
       <c r="B289" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>136377407</v>
       </c>
       <c r="B290" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>136383403</v>
       </c>
       <c r="B291" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>136384834</v>
       </c>
       <c r="B292" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>136386076</v>
       </c>
       <c r="B293" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>136392711</v>
       </c>
       <c r="B294" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>136392716</v>
       </c>
       <c r="B295" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>136392718</v>
       </c>
       <c r="B296" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>136392722</v>
       </c>
       <c r="B297" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>136392734</v>
       </c>
       <c r="B298" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>136392736</v>
       </c>
       <c r="B299" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>136392751</v>
       </c>
       <c r="B300" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>136392781</v>
       </c>
       <c r="B301" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>136392782</v>
       </c>
       <c r="B302" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>136392785</v>
       </c>
       <c r="B303" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>136392826</v>
       </c>
       <c r="B304" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>136393474</v>
       </c>
       <c r="B305" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>136396121</v>
       </c>
       <c r="B306" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>136402418</v>
       </c>
       <c r="B307" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>136392761</v>
       </c>
       <c r="B310" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>136402424</v>
       </c>
       <c r="B311" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>136392810</v>
       </c>
       <c r="B316" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>136392787</v>
       </c>
       <c r="B317" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>136396123</v>
       </c>
       <c r="B318" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>136392749</v>
       </c>
       <c r="B319" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>136377218</v>
       </c>
       <c r="B332" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>136383007</v>
       </c>
       <c r="B333" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>136392743</v>
       </c>
       <c r="B334" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>136392745</v>
       </c>
       <c r="B335" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>136392747</v>
       </c>
       <c r="B336" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>136392754</v>
       </c>
       <c r="B337" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>136392763</v>
       </c>
       <c r="B338" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>136393470</v>
       </c>
       <c r="B339" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>136393488</v>
       </c>
       <c r="B340" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>136393491</v>
       </c>
       <c r="B341" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>136393501</v>
       </c>
       <c r="B342" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>136393514</v>
       </c>
       <c r="B343" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>136393517</v>
       </c>
       <c r="B344" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>136393523</v>
       </c>
       <c r="B345" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>136396151</v>
       </c>
       <c r="B346" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>136396157</v>
       </c>
       <c r="B347" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>136402410</v>
       </c>
       <c r="B348" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>136402417</v>
       </c>
       <c r="B349" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>136402432</v>
       </c>
       <c r="B350" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>136402444</v>
       </c>
       <c r="B351" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>136392748</v>
       </c>
       <c r="B353" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>136392799</v>
       </c>
       <c r="B354" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>136392801</v>
       </c>
       <c r="B355" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>136392806</v>
       </c>
       <c r="B356" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>136396116</v>
       </c>
       <c r="B357" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>136402440</v>
       </c>
       <c r="B358" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>136392770</v>
       </c>
       <c r="B360" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>136392776</v>
       </c>
       <c r="B361" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>136402425</v>
       </c>
       <c r="B362" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136402433</v>
       </c>
       <c r="B2" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136392821</v>
       </c>
       <c r="B16" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136396104</v>
       </c>
       <c r="B17" t="n">
-        <v>91887</v>
+        <v>91889</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136386035</v>
       </c>
       <c r="B18" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>136376836</v>
       </c>
       <c r="B19" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136380121</v>
       </c>
       <c r="B20" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>136381954</v>
       </c>
       <c r="B21" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>136384925</v>
       </c>
       <c r="B22" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>136386039</v>
       </c>
       <c r="B23" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>136386054</v>
       </c>
       <c r="B24" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>136386055</v>
       </c>
       <c r="B25" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>136386073</v>
       </c>
       <c r="B26" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>136386075</v>
       </c>
       <c r="B27" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>136386082</v>
       </c>
       <c r="B28" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>136386084</v>
       </c>
       <c r="B29" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136386090</v>
       </c>
       <c r="B30" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136392727</v>
       </c>
       <c r="B31" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136392735</v>
       </c>
       <c r="B32" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136392741</v>
       </c>
       <c r="B33" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>136392756</v>
       </c>
       <c r="B34" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136392771</v>
       </c>
       <c r="B35" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136392794</v>
       </c>
       <c r="B36" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136392800</v>
       </c>
       <c r="B37" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136392803</v>
       </c>
       <c r="B38" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136392811</v>
       </c>
       <c r="B39" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136392812</v>
       </c>
       <c r="B40" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>136392813</v>
       </c>
       <c r="B41" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>136392823</v>
       </c>
       <c r="B42" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>136392828</v>
       </c>
       <c r="B43" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>136393469</v>
       </c>
       <c r="B44" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>136396101</v>
       </c>
       <c r="B45" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>136396122</v>
       </c>
       <c r="B46" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>136396125</v>
       </c>
       <c r="B47" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>136396129</v>
       </c>
       <c r="B48" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>136396130</v>
       </c>
       <c r="B49" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>136396135</v>
       </c>
       <c r="B50" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>136396148</v>
       </c>
       <c r="B51" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>136396149</v>
       </c>
       <c r="B52" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>136396152</v>
       </c>
       <c r="B53" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>136396154</v>
       </c>
       <c r="B54" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136396155</v>
       </c>
       <c r="B55" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>136396156</v>
       </c>
       <c r="B56" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>136402412</v>
       </c>
       <c r="B57" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>136402421</v>
       </c>
       <c r="B58" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>136402428</v>
       </c>
       <c r="B59" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136402429</v>
       </c>
       <c r="B60" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136402434</v>
       </c>
       <c r="B61" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>136402436</v>
       </c>
       <c r="B62" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>136402438</v>
       </c>
       <c r="B63" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>136402439</v>
       </c>
       <c r="B64" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136402441</v>
       </c>
       <c r="B65" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>136402442</v>
       </c>
       <c r="B66" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>136405164</v>
       </c>
       <c r="B67" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136402408</v>
       </c>
       <c r="B68" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>136386041</v>
       </c>
       <c r="B69" t="n">
-        <v>89318</v>
+        <v>89320</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>136386050</v>
       </c>
       <c r="B70" t="n">
-        <v>89318</v>
+        <v>89320</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>136392816</v>
       </c>
       <c r="B71" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>136402409</v>
       </c>
       <c r="B72" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>136382713</v>
       </c>
       <c r="B75" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136392764</v>
       </c>
       <c r="B76" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>136396142</v>
       </c>
       <c r="B77" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>136396143</v>
       </c>
       <c r="B78" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>136402426</v>
       </c>
       <c r="B79" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>136402422</v>
       </c>
       <c r="B80" t="n">
-        <v>91465</v>
+        <v>91467</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>136392786</v>
       </c>
       <c r="B81" t="n">
-        <v>93393</v>
+        <v>93395</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>136392810</v>
       </c>
       <c r="B316" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>136392787</v>
       </c>
       <c r="B317" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>136396123</v>
       </c>
       <c r="B318" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>136392749</v>
       </c>
       <c r="B319" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136402433</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136392725</v>
       </c>
       <c r="B3" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136379790</v>
       </c>
       <c r="B4" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136384395</v>
       </c>
       <c r="B5" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136392737</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>136392768</v>
       </c>
       <c r="B7" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136392775</v>
       </c>
       <c r="B8" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>136392792</v>
       </c>
       <c r="B9" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136392793</v>
       </c>
       <c r="B10" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>136396115</v>
       </c>
       <c r="B11" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>136396133</v>
       </c>
       <c r="B12" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>136402411</v>
       </c>
       <c r="B13" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>136402419</v>
       </c>
       <c r="B14" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136402423</v>
       </c>
       <c r="B15" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136392821</v>
       </c>
       <c r="B16" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136396104</v>
       </c>
       <c r="B17" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136386035</v>
       </c>
       <c r="B18" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>136376836</v>
       </c>
       <c r="B19" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136380121</v>
       </c>
       <c r="B20" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>136381954</v>
       </c>
       <c r="B21" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>136384925</v>
       </c>
       <c r="B22" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>136386039</v>
       </c>
       <c r="B23" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>136386054</v>
       </c>
       <c r="B24" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>136386055</v>
       </c>
       <c r="B25" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>136386073</v>
       </c>
       <c r="B26" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>136386075</v>
       </c>
       <c r="B27" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>136386082</v>
       </c>
       <c r="B28" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>136386084</v>
       </c>
       <c r="B29" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136386090</v>
       </c>
       <c r="B30" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136392727</v>
       </c>
       <c r="B31" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136392735</v>
       </c>
       <c r="B32" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136392741</v>
       </c>
       <c r="B33" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>136392756</v>
       </c>
       <c r="B34" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136392771</v>
       </c>
       <c r="B35" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136392794</v>
       </c>
       <c r="B36" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136392800</v>
       </c>
       <c r="B37" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136392803</v>
       </c>
       <c r="B38" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136392811</v>
       </c>
       <c r="B39" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136392812</v>
       </c>
       <c r="B40" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>136392813</v>
       </c>
       <c r="B41" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>136392823</v>
       </c>
       <c r="B42" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>136392828</v>
       </c>
       <c r="B43" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>136393469</v>
       </c>
       <c r="B44" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>136396101</v>
       </c>
       <c r="B45" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>136396122</v>
       </c>
       <c r="B46" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>136396125</v>
       </c>
       <c r="B47" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>136396129</v>
       </c>
       <c r="B48" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>136396130</v>
       </c>
       <c r="B49" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>136396135</v>
       </c>
       <c r="B50" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>136396148</v>
       </c>
       <c r="B51" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>136396149</v>
       </c>
       <c r="B52" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>136396152</v>
       </c>
       <c r="B53" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>136396154</v>
       </c>
       <c r="B54" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136396155</v>
       </c>
       <c r="B55" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>136396156</v>
       </c>
       <c r="B56" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>136402412</v>
       </c>
       <c r="B57" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>136402421</v>
       </c>
       <c r="B58" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>136402428</v>
       </c>
       <c r="B59" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136402429</v>
       </c>
       <c r="B60" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136402434</v>
       </c>
       <c r="B61" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>136402436</v>
       </c>
       <c r="B62" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>136402438</v>
       </c>
       <c r="B63" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>136402439</v>
       </c>
       <c r="B64" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136402441</v>
       </c>
       <c r="B65" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>136402442</v>
       </c>
       <c r="B66" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>136405164</v>
       </c>
       <c r="B67" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136402408</v>
       </c>
       <c r="B68" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>136386041</v>
       </c>
       <c r="B69" t="n">
-        <v>89320</v>
+        <v>89322</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>136386050</v>
       </c>
       <c r="B70" t="n">
-        <v>89320</v>
+        <v>89322</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>136392816</v>
       </c>
       <c r="B71" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>136402409</v>
       </c>
       <c r="B72" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>136382713</v>
       </c>
       <c r="B75" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136392764</v>
       </c>
       <c r="B76" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>136396142</v>
       </c>
       <c r="B77" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>136396143</v>
       </c>
       <c r="B78" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>136402426</v>
       </c>
       <c r="B79" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>136402422</v>
       </c>
       <c r="B80" t="n">
-        <v>91467</v>
+        <v>91469</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>136392786</v>
       </c>
       <c r="B81" t="n">
-        <v>93395</v>
+        <v>93397</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>136376332</v>
       </c>
       <c r="B108" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>136376665</v>
       </c>
       <c r="B109" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>136377035</v>
       </c>
       <c r="B110" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>136382303</v>
       </c>
       <c r="B111" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>136386037</v>
       </c>
       <c r="B112" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>136386040</v>
       </c>
       <c r="B113" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>136386051</v>
       </c>
       <c r="B114" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>136386056</v>
       </c>
       <c r="B115" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136386057</v>
       </c>
       <c r="B116" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136386058</v>
       </c>
       <c r="B117" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136386059</v>
       </c>
       <c r="B118" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136386060</v>
       </c>
       <c r="B119" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136386061</v>
       </c>
       <c r="B120" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>136386064</v>
       </c>
       <c r="B121" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>136386066</v>
       </c>
       <c r="B122" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>136386067</v>
       </c>
       <c r="B123" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>136386070</v>
       </c>
       <c r="B124" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>136386071</v>
       </c>
       <c r="B125" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>136386072</v>
       </c>
       <c r="B126" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>136386087</v>
       </c>
       <c r="B127" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>136386089</v>
       </c>
       <c r="B128" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>136392705</v>
       </c>
       <c r="B129" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>136392738</v>
       </c>
       <c r="B130" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>136392752</v>
       </c>
       <c r="B131" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>136392755</v>
       </c>
       <c r="B132" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>136392757</v>
       </c>
       <c r="B133" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>136392769</v>
       </c>
       <c r="B134" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>136392772</v>
       </c>
       <c r="B135" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>136392773</v>
       </c>
       <c r="B136" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>136392779</v>
       </c>
       <c r="B137" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>136392780</v>
       </c>
       <c r="B138" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>136392790</v>
       </c>
       <c r="B139" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>136392795</v>
       </c>
       <c r="B140" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>136392796</v>
       </c>
       <c r="B141" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>136392805</v>
       </c>
       <c r="B142" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>136392818</v>
       </c>
       <c r="B143" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>136392820</v>
       </c>
       <c r="B144" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>136392827</v>
       </c>
       <c r="B145" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>136392829</v>
       </c>
       <c r="B146" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>136393453</v>
       </c>
       <c r="B147" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>136393455</v>
       </c>
       <c r="B148" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>136393456</v>
       </c>
       <c r="B149" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>136393458</v>
       </c>
       <c r="B150" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>136393459</v>
       </c>
       <c r="B151" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>136393460</v>
       </c>
       <c r="B152" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>136393461</v>
       </c>
       <c r="B153" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>136393462</v>
       </c>
       <c r="B154" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>136393463</v>
       </c>
       <c r="B155" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>136393464</v>
       </c>
       <c r="B156" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>136393465</v>
       </c>
       <c r="B157" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>136393468</v>
       </c>
       <c r="B158" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>136393472</v>
       </c>
       <c r="B159" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>136393475</v>
       </c>
       <c r="B160" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>136393482</v>
       </c>
       <c r="B161" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>136393483</v>
       </c>
       <c r="B162" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>136393484</v>
       </c>
       <c r="B163" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>136393485</v>
       </c>
       <c r="B164" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>136393489</v>
       </c>
       <c r="B165" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>136393490</v>
       </c>
       <c r="B166" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>136393492</v>
       </c>
       <c r="B167" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>136393493</v>
       </c>
       <c r="B168" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>136393496</v>
       </c>
       <c r="B169" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>136393497</v>
       </c>
       <c r="B170" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>136393498</v>
       </c>
       <c r="B171" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>136393500</v>
       </c>
       <c r="B172" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>136393503</v>
       </c>
       <c r="B173" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>136393505</v>
       </c>
       <c r="B174" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>136393506</v>
       </c>
       <c r="B175" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>136393509</v>
       </c>
       <c r="B176" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>136393512</v>
       </c>
       <c r="B177" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>136393515</v>
       </c>
       <c r="B178" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>136393518</v>
       </c>
       <c r="B179" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>136393519</v>
       </c>
       <c r="B180" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>136393520</v>
       </c>
       <c r="B181" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>136393524</v>
       </c>
       <c r="B182" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>136393525</v>
       </c>
       <c r="B183" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>136393527</v>
       </c>
       <c r="B184" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>136396107</v>
       </c>
       <c r="B185" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>136396109</v>
       </c>
       <c r="B186" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>136396112</v>
       </c>
       <c r="B187" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>136396113</v>
       </c>
       <c r="B188" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>136396118</v>
       </c>
       <c r="B189" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>136396119</v>
       </c>
       <c r="B190" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>136396128</v>
       </c>
       <c r="B191" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>136396132</v>
       </c>
       <c r="B192" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>136396136</v>
       </c>
       <c r="B193" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>136396138</v>
       </c>
       <c r="B194" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>136396140</v>
       </c>
       <c r="B195" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>136396145</v>
       </c>
       <c r="B196" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>136396150</v>
       </c>
       <c r="B197" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>136396159</v>
       </c>
       <c r="B198" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>136402413</v>
       </c>
       <c r="B199" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>136402430</v>
       </c>
       <c r="B200" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>136386074</v>
       </c>
       <c r="B201" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>136392732</v>
       </c>
       <c r="B202" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>136392798</v>
       </c>
       <c r="B203" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>136383035</v>
       </c>
       <c r="B219" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>136386044</v>
       </c>
       <c r="B220" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>136386047</v>
       </c>
       <c r="B221" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>136386053</v>
       </c>
       <c r="B222" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>136386062</v>
       </c>
       <c r="B223" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>136386069</v>
       </c>
       <c r="B224" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>136386077</v>
       </c>
       <c r="B225" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>136392744</v>
       </c>
       <c r="B226" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>136392746</v>
       </c>
       <c r="B227" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>136393467</v>
       </c>
       <c r="B228" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>136393476</v>
       </c>
       <c r="B229" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>136393487</v>
       </c>
       <c r="B230" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>136393502</v>
       </c>
       <c r="B231" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>136393504</v>
       </c>
       <c r="B232" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>136393513</v>
       </c>
       <c r="B233" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>136393516</v>
       </c>
       <c r="B234" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>136393522</v>
       </c>
       <c r="B235" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>136396153</v>
       </c>
       <c r="B236" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>136402414</v>
       </c>
       <c r="B237" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>136402437</v>
       </c>
       <c r="B238" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>136386042</v>
       </c>
       <c r="B241" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>136386043</v>
       </c>
       <c r="B242" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>136386045</v>
       </c>
       <c r="B243" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>136386048</v>
       </c>
       <c r="B244" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>136386052</v>
       </c>
       <c r="B245" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>136386063</v>
       </c>
       <c r="B246" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>136386065</v>
       </c>
       <c r="B247" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>136386068</v>
       </c>
       <c r="B248" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>136386078</v>
       </c>
       <c r="B249" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>136386081</v>
       </c>
       <c r="B250" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>136386083</v>
       </c>
       <c r="B251" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>136392720</v>
       </c>
       <c r="B252" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>136392742</v>
       </c>
       <c r="B253" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>136392753</v>
       </c>
       <c r="B254" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>136392804</v>
       </c>
       <c r="B255" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>136393486</v>
       </c>
       <c r="B256" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>136393508</v>
       </c>
       <c r="B257" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>136393510</v>
       </c>
       <c r="B258" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>136396158</v>
       </c>
       <c r="B259" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>136402420</v>
       </c>
       <c r="B260" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>136392810</v>
       </c>
       <c r="B316" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>136392787</v>
       </c>
       <c r="B317" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>136396123</v>
       </c>
       <c r="B318" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>136392749</v>
       </c>
       <c r="B319" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>136377218</v>
       </c>
       <c r="B332" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>136383007</v>
       </c>
       <c r="B333" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>136392743</v>
       </c>
       <c r="B334" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>136392745</v>
       </c>
       <c r="B335" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>136392747</v>
       </c>
       <c r="B336" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>136392754</v>
       </c>
       <c r="B337" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>136392763</v>
       </c>
       <c r="B338" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>136393470</v>
       </c>
       <c r="B339" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>136393488</v>
       </c>
       <c r="B340" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>136393491</v>
       </c>
       <c r="B341" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>136393501</v>
       </c>
       <c r="B342" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>136393514</v>
       </c>
       <c r="B343" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>136393517</v>
       </c>
       <c r="B344" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>136393523</v>
       </c>
       <c r="B345" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>136396151</v>
       </c>
       <c r="B346" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>136396157</v>
       </c>
       <c r="B347" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>136402410</v>
       </c>
       <c r="B348" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>136402417</v>
       </c>
       <c r="B349" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>136402432</v>
       </c>
       <c r="B350" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>136402444</v>
       </c>
       <c r="B351" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>136392748</v>
       </c>
       <c r="B353" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>136392799</v>
       </c>
       <c r="B354" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>136392801</v>
       </c>
       <c r="B355" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>136392806</v>
       </c>
       <c r="B356" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>136396116</v>
       </c>
       <c r="B357" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>136402440</v>
       </c>
       <c r="B358" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>136392770</v>
       </c>
       <c r="B360" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>136392776</v>
       </c>
       <c r="B361" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>136402425</v>
       </c>
       <c r="B362" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136402433</v>
       </c>
       <c r="B2" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136392725</v>
       </c>
       <c r="B3" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136379790</v>
       </c>
       <c r="B4" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136384395</v>
       </c>
       <c r="B5" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136392737</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>136392768</v>
       </c>
       <c r="B7" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136392775</v>
       </c>
       <c r="B8" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>136392792</v>
       </c>
       <c r="B9" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136392793</v>
       </c>
       <c r="B10" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>136396115</v>
       </c>
       <c r="B11" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>136396133</v>
       </c>
       <c r="B12" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>136402411</v>
       </c>
       <c r="B13" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>136402419</v>
       </c>
       <c r="B14" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136402423</v>
       </c>
       <c r="B15" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136392821</v>
       </c>
       <c r="B16" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136396104</v>
       </c>
       <c r="B17" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136386035</v>
       </c>
       <c r="B18" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>136376836</v>
       </c>
       <c r="B19" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136380121</v>
       </c>
       <c r="B20" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>136381954</v>
       </c>
       <c r="B21" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>136384925</v>
       </c>
       <c r="B22" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>136386039</v>
       </c>
       <c r="B23" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>136386054</v>
       </c>
       <c r="B24" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>136386055</v>
       </c>
       <c r="B25" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>136386073</v>
       </c>
       <c r="B26" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>136386075</v>
       </c>
       <c r="B27" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>136386082</v>
       </c>
       <c r="B28" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>136386084</v>
       </c>
       <c r="B29" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136386090</v>
       </c>
       <c r="B30" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136392727</v>
       </c>
       <c r="B31" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136392735</v>
       </c>
       <c r="B32" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136392741</v>
       </c>
       <c r="B33" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>136392756</v>
       </c>
       <c r="B34" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136392771</v>
       </c>
       <c r="B35" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136392794</v>
       </c>
       <c r="B36" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136392800</v>
       </c>
       <c r="B37" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136392803</v>
       </c>
       <c r="B38" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136392811</v>
       </c>
       <c r="B39" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136392812</v>
       </c>
       <c r="B40" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>136392813</v>
       </c>
       <c r="B41" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>136392823</v>
       </c>
       <c r="B42" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>136392828</v>
       </c>
       <c r="B43" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>136393469</v>
       </c>
       <c r="B44" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>136396101</v>
       </c>
       <c r="B45" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>136396122</v>
       </c>
       <c r="B46" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>136396125</v>
       </c>
       <c r="B47" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>136396129</v>
       </c>
       <c r="B48" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>136396130</v>
       </c>
       <c r="B49" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>136396135</v>
       </c>
       <c r="B50" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>136396148</v>
       </c>
       <c r="B51" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>136396149</v>
       </c>
       <c r="B52" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>136396152</v>
       </c>
       <c r="B53" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>136396154</v>
       </c>
       <c r="B54" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136396155</v>
       </c>
       <c r="B55" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>136396156</v>
       </c>
       <c r="B56" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>136402412</v>
       </c>
       <c r="B57" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>136402421</v>
       </c>
       <c r="B58" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>136402428</v>
       </c>
       <c r="B59" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136402429</v>
       </c>
       <c r="B60" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136402434</v>
       </c>
       <c r="B61" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>136402436</v>
       </c>
       <c r="B62" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>136402438</v>
       </c>
       <c r="B63" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>136402439</v>
       </c>
       <c r="B64" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136402441</v>
       </c>
       <c r="B65" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>136402442</v>
       </c>
       <c r="B66" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>136405164</v>
       </c>
       <c r="B67" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136402408</v>
       </c>
       <c r="B68" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>136386041</v>
       </c>
       <c r="B69" t="n">
-        <v>89322</v>
+        <v>89324</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>136386050</v>
       </c>
       <c r="B70" t="n">
-        <v>89322</v>
+        <v>89324</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>136392816</v>
       </c>
       <c r="B71" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>136402409</v>
       </c>
       <c r="B72" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>136382713</v>
       </c>
       <c r="B75" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136392764</v>
       </c>
       <c r="B76" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>136396142</v>
       </c>
       <c r="B77" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>136396143</v>
       </c>
       <c r="B78" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>136402426</v>
       </c>
       <c r="B79" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>136402422</v>
       </c>
       <c r="B80" t="n">
-        <v>91469</v>
+        <v>91471</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>136392786</v>
       </c>
       <c r="B81" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>136376332</v>
       </c>
       <c r="B108" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>136376665</v>
       </c>
       <c r="B109" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>136377035</v>
       </c>
       <c r="B110" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>136382303</v>
       </c>
       <c r="B111" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>136386037</v>
       </c>
       <c r="B112" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>136386040</v>
       </c>
       <c r="B113" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>136386051</v>
       </c>
       <c r="B114" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>136386056</v>
       </c>
       <c r="B115" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136386057</v>
       </c>
       <c r="B116" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136386058</v>
       </c>
       <c r="B117" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136386059</v>
       </c>
       <c r="B118" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136386060</v>
       </c>
       <c r="B119" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136386061</v>
       </c>
       <c r="B120" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>136386064</v>
       </c>
       <c r="B121" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>136386066</v>
       </c>
       <c r="B122" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>136386067</v>
       </c>
       <c r="B123" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>136386070</v>
       </c>
       <c r="B124" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>136386071</v>
       </c>
       <c r="B125" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>136386072</v>
       </c>
       <c r="B126" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>136386087</v>
       </c>
       <c r="B127" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>136386089</v>
       </c>
       <c r="B128" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>136392705</v>
       </c>
       <c r="B129" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>136392738</v>
       </c>
       <c r="B130" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>136392752</v>
       </c>
       <c r="B131" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>136392755</v>
       </c>
       <c r="B132" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>136392757</v>
       </c>
       <c r="B133" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>136392769</v>
       </c>
       <c r="B134" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>136392772</v>
       </c>
       <c r="B135" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>136392773</v>
       </c>
       <c r="B136" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>136392779</v>
       </c>
       <c r="B137" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>136392780</v>
       </c>
       <c r="B138" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>136392790</v>
       </c>
       <c r="B139" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>136392795</v>
       </c>
       <c r="B140" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>136392796</v>
       </c>
       <c r="B141" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>136392805</v>
       </c>
       <c r="B142" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>136392818</v>
       </c>
       <c r="B143" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>136392820</v>
       </c>
       <c r="B144" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>136392827</v>
       </c>
       <c r="B145" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>136392829</v>
       </c>
       <c r="B146" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>136393453</v>
       </c>
       <c r="B147" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>136393455</v>
       </c>
       <c r="B148" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>136393456</v>
       </c>
       <c r="B149" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>136393458</v>
       </c>
       <c r="B150" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>136393459</v>
       </c>
       <c r="B151" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>136393460</v>
       </c>
       <c r="B152" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>136393461</v>
       </c>
       <c r="B153" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>136393462</v>
       </c>
       <c r="B154" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>136393463</v>
       </c>
       <c r="B155" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>136393464</v>
       </c>
       <c r="B156" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>136393465</v>
       </c>
       <c r="B157" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>136393468</v>
       </c>
       <c r="B158" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>136393472</v>
       </c>
       <c r="B159" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>136393475</v>
       </c>
       <c r="B160" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>136393482</v>
       </c>
       <c r="B161" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>136393483</v>
       </c>
       <c r="B162" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>136393484</v>
       </c>
       <c r="B163" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>136393485</v>
       </c>
       <c r="B164" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>136393489</v>
       </c>
       <c r="B165" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>136393490</v>
       </c>
       <c r="B166" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>136393492</v>
       </c>
       <c r="B167" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>136393493</v>
       </c>
       <c r="B168" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>136393496</v>
       </c>
       <c r="B169" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>136393497</v>
       </c>
       <c r="B170" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>136393498</v>
       </c>
       <c r="B171" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>136393500</v>
       </c>
       <c r="B172" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>136393503</v>
       </c>
       <c r="B173" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>136393505</v>
       </c>
       <c r="B174" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>136393506</v>
       </c>
       <c r="B175" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>136393509</v>
       </c>
       <c r="B176" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>136393512</v>
       </c>
       <c r="B177" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>136393515</v>
       </c>
       <c r="B178" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>136393518</v>
       </c>
       <c r="B179" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>136393519</v>
       </c>
       <c r="B180" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>136393520</v>
       </c>
       <c r="B181" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>136393524</v>
       </c>
       <c r="B182" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>136393525</v>
       </c>
       <c r="B183" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>136393527</v>
       </c>
       <c r="B184" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>136396107</v>
       </c>
       <c r="B185" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>136396109</v>
       </c>
       <c r="B186" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>136396112</v>
       </c>
       <c r="B187" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>136396113</v>
       </c>
       <c r="B188" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>136396118</v>
       </c>
       <c r="B189" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>136396119</v>
       </c>
       <c r="B190" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>136396128</v>
       </c>
       <c r="B191" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>136396132</v>
       </c>
       <c r="B192" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>136396136</v>
       </c>
       <c r="B193" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>136396138</v>
       </c>
       <c r="B194" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>136396140</v>
       </c>
       <c r="B195" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>136396145</v>
       </c>
       <c r="B196" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>136396150</v>
       </c>
       <c r="B197" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>136396159</v>
       </c>
       <c r="B198" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>136402413</v>
       </c>
       <c r="B199" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>136402430</v>
       </c>
       <c r="B200" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>136386074</v>
       </c>
       <c r="B201" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>136392732</v>
       </c>
       <c r="B202" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>136392798</v>
       </c>
       <c r="B203" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>136383035</v>
       </c>
       <c r="B219" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>136386044</v>
       </c>
       <c r="B220" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>136386047</v>
       </c>
       <c r="B221" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>136386053</v>
       </c>
       <c r="B222" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>136386062</v>
       </c>
       <c r="B223" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>136386069</v>
       </c>
       <c r="B224" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>136386077</v>
       </c>
       <c r="B225" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>136392744</v>
       </c>
       <c r="B226" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>136392746</v>
       </c>
       <c r="B227" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>136393467</v>
       </c>
       <c r="B228" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>136393476</v>
       </c>
       <c r="B229" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>136393487</v>
       </c>
       <c r="B230" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>136393502</v>
       </c>
       <c r="B231" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>136393504</v>
       </c>
       <c r="B232" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>136393513</v>
       </c>
       <c r="B233" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>136393516</v>
       </c>
       <c r="B234" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>136393522</v>
       </c>
       <c r="B235" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>136396153</v>
       </c>
       <c r="B236" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>136402414</v>
       </c>
       <c r="B237" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>136402437</v>
       </c>
       <c r="B238" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>136386042</v>
       </c>
       <c r="B241" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>136386043</v>
       </c>
       <c r="B242" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>136386045</v>
       </c>
       <c r="B243" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>136386048</v>
       </c>
       <c r="B244" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>136386052</v>
       </c>
       <c r="B245" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>136386063</v>
       </c>
       <c r="B246" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>136386065</v>
       </c>
       <c r="B247" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>136386068</v>
       </c>
       <c r="B248" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>136386078</v>
       </c>
       <c r="B249" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>136386081</v>
       </c>
       <c r="B250" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>136386083</v>
       </c>
       <c r="B251" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>136392720</v>
       </c>
       <c r="B252" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>136392742</v>
       </c>
       <c r="B253" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>136392753</v>
       </c>
       <c r="B254" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>136392804</v>
       </c>
       <c r="B255" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>136393486</v>
       </c>
       <c r="B256" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>136393508</v>
       </c>
       <c r="B257" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>136393510</v>
       </c>
       <c r="B258" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>136396158</v>
       </c>
       <c r="B259" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>136402420</v>
       </c>
       <c r="B260" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>136392810</v>
       </c>
       <c r="B316" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>136392787</v>
       </c>
       <c r="B317" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>136396123</v>
       </c>
       <c r="B318" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>136392749</v>
       </c>
       <c r="B319" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>136377218</v>
       </c>
       <c r="B332" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>136383007</v>
       </c>
       <c r="B333" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>136392743</v>
       </c>
       <c r="B334" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>136392745</v>
       </c>
       <c r="B335" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>136392747</v>
       </c>
       <c r="B336" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>136392754</v>
       </c>
       <c r="B337" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>136392763</v>
       </c>
       <c r="B338" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>136393470</v>
       </c>
       <c r="B339" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>136393488</v>
       </c>
       <c r="B340" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>136393491</v>
       </c>
       <c r="B341" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>136393501</v>
       </c>
       <c r="B342" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>136393514</v>
       </c>
       <c r="B343" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>136393517</v>
       </c>
       <c r="B344" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>136393523</v>
       </c>
       <c r="B345" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>136396151</v>
       </c>
       <c r="B346" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>136396157</v>
       </c>
       <c r="B347" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>136402410</v>
       </c>
       <c r="B348" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>136402417</v>
       </c>
       <c r="B349" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>136402432</v>
       </c>
       <c r="B350" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>136402444</v>
       </c>
       <c r="B351" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>136392748</v>
       </c>
       <c r="B353" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>136392799</v>
       </c>
       <c r="B354" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>136392801</v>
       </c>
       <c r="B355" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>136392806</v>
       </c>
       <c r="B356" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>136396116</v>
       </c>
       <c r="B357" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>136402440</v>
       </c>
       <c r="B358" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>136392770</v>
       </c>
       <c r="B360" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>136392776</v>
       </c>
       <c r="B361" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>136402425</v>
       </c>
       <c r="B362" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136402433</v>
       </c>
       <c r="B2" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>136402411</v>
       </c>
       <c r="B13" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>136402419</v>
       </c>
       <c r="B14" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136402423</v>
       </c>
       <c r="B15" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>136402412</v>
       </c>
       <c r="B57" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>136402421</v>
       </c>
       <c r="B58" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>136402428</v>
       </c>
       <c r="B59" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136402429</v>
       </c>
       <c r="B60" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136402434</v>
       </c>
       <c r="B61" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>136402436</v>
       </c>
       <c r="B62" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>136402438</v>
       </c>
       <c r="B63" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>136402439</v>
       </c>
       <c r="B64" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136402441</v>
       </c>
       <c r="B65" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>136402442</v>
       </c>
       <c r="B66" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>136405164</v>
       </c>
       <c r="B67" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136402408</v>
       </c>
       <c r="B68" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>136402409</v>
       </c>
       <c r="B72" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>136402426</v>
       </c>
       <c r="B79" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>136402422</v>
       </c>
       <c r="B80" t="n">
-        <v>91471</v>
+        <v>91472</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>136402413</v>
       </c>
       <c r="B199" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>136402430</v>
       </c>
       <c r="B200" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>136402414</v>
       </c>
       <c r="B237" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>136402437</v>
       </c>
       <c r="B238" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>136402420</v>
       </c>
       <c r="B260" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>136402410</v>
       </c>
       <c r="B348" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>136402417</v>
       </c>
       <c r="B349" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>136402432</v>
       </c>
       <c r="B350" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>136402444</v>
       </c>
       <c r="B351" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>136402440</v>
       </c>
       <c r="B358" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>136402425</v>
       </c>
       <c r="B362" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2676,10 +2676,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136376836</v>
+        <v>137209411</v>
       </c>
       <c r="B19" t="n">
-        <v>93415</v>
+        <v>93435</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2687,26 +2687,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2714,24 +2714,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Dlr</t>
+          <t>Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428397</v>
+        <v>428320</v>
       </c>
       <c r="R19" t="n">
-        <v>6799733</v>
+        <v>6799640</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2755,22 +2752,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flera ex, ej räknat noga, men minst tio. På samma plats där 2 ex av blå taggsvamp noterats tidigare i september i år. Fruktkropparna var nu bruna av ålder, så skicket gör att dekan vara svåra att arta. Enligt  Björnström/Wikström "Kalkbarrskogens marksvampar" har äldre ex bruna taggar med ljus spets och kan utveckla "lurvig hattyta" och tappa sin blå färg (s 72). På ett av fotona kan man fortfarande se orange färg som är kvar i foten, så sammantaget bör det vara blå taggsvamp.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2779,30 +2781,31 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136376836</t>
+          <t>https://artportalen.se/Sighting/137209411</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136380121</v>
+        <v>136376836</v>
       </c>
       <c r="B20" t="n">
         <v>93415</v>
@@ -2832,7 +2835,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2840,19 +2843,24 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428356</v>
+        <v>428397</v>
       </c>
       <c r="R20" t="n">
-        <v>6799680</v>
+        <v>6799733</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2881,7 +2889,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2891,7 +2899,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2917,13 +2925,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136380121</t>
+          <t>https://artportalen.se/Sighting/136376836</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136381954</v>
+        <v>136380121</v>
       </c>
       <c r="B21" t="n">
         <v>93415</v>
@@ -2953,7 +2961,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2961,24 +2969,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428810</v>
+        <v>428356</v>
       </c>
       <c r="R21" t="n">
-        <v>6800214</v>
+        <v>6799680</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3007,7 +3010,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3017,7 +3020,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3043,13 +3046,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136381954</t>
+          <t>https://artportalen.se/Sighting/136380121</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136384925</v>
+        <v>136381954</v>
       </c>
       <c r="B22" t="n">
         <v>93415</v>
@@ -3079,7 +3082,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3094,14 +3097,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428499</v>
+        <v>428810</v>
       </c>
       <c r="R22" t="n">
-        <v>6799626</v>
+        <v>6800214</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3133,7 +3136,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3143,7 +3146,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3169,13 +3172,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136384925</t>
+          <t>https://artportalen.se/Sighting/136381954</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136386039</v>
+        <v>136384925</v>
       </c>
       <c r="B23" t="n">
         <v>93415</v>
@@ -3205,7 +3208,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3213,16 +3216,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428299</v>
+        <v>428499</v>
       </c>
       <c r="R23" t="n">
-        <v>6799775</v>
+        <v>6799626</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3254,7 +3262,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3264,7 +3272,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3279,24 +3287,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136386039</t>
+          <t>https://artportalen.se/Sighting/136384925</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136386054</v>
+        <v>136386039</v>
       </c>
       <c r="B24" t="n">
         <v>93415</v>
@@ -3326,7 +3334,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3340,10 +3348,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428279</v>
+        <v>428299</v>
       </c>
       <c r="R24" t="n">
-        <v>6800168</v>
+        <v>6799775</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3375,7 +3383,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3385,7 +3393,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3411,13 +3419,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136386054</t>
+          <t>https://artportalen.se/Sighting/136386039</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136386055</v>
+        <v>136386054</v>
       </c>
       <c r="B25" t="n">
         <v>93415</v>
@@ -3447,7 +3455,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3461,10 +3469,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428218</v>
+        <v>428279</v>
       </c>
       <c r="R25" t="n">
-        <v>6800124</v>
+        <v>6800168</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3496,7 +3504,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3506,7 +3514,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3532,13 +3540,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136386055</t>
+          <t>https://artportalen.se/Sighting/136386054</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136386073</v>
+        <v>136386055</v>
       </c>
       <c r="B26" t="n">
         <v>93415</v>
@@ -3568,12 +3576,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3582,10 +3590,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428610</v>
+        <v>428218</v>
       </c>
       <c r="R26" t="n">
-        <v>6799718</v>
+        <v>6800124</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3617,7 +3625,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3627,7 +3635,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3653,13 +3661,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136386073</t>
+          <t>https://artportalen.se/Sighting/136386055</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136386075</v>
+        <v>136386073</v>
       </c>
       <c r="B27" t="n">
         <v>93415</v>
@@ -3689,7 +3697,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3703,10 +3711,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>428623</v>
+        <v>428610</v>
       </c>
       <c r="R27" t="n">
-        <v>6799698</v>
+        <v>6799718</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3738,7 +3746,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3748,7 +3756,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3774,13 +3782,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136386075</t>
+          <t>https://artportalen.se/Sighting/136386073</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136386082</v>
+        <v>136386075</v>
       </c>
       <c r="B28" t="n">
         <v>93415</v>
@@ -3810,12 +3818,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3824,13 +3832,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428704</v>
+        <v>428623</v>
       </c>
       <c r="R28" t="n">
-        <v>6799717</v>
+        <v>6799698</v>
       </c>
       <c r="S28" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3859,7 +3867,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3869,7 +3877,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3895,13 +3903,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136386082</t>
+          <t>https://artportalen.se/Sighting/136386075</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136386084</v>
+        <v>136386082</v>
       </c>
       <c r="B29" t="n">
         <v>93415</v>
@@ -3931,7 +3939,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3945,13 +3953,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428534</v>
+        <v>428704</v>
       </c>
       <c r="R29" t="n">
-        <v>6799576</v>
+        <v>6799717</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3980,7 +3988,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3990,7 +3998,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4016,13 +4024,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136386084</t>
+          <t>https://artportalen.se/Sighting/136386082</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136386090</v>
+        <v>136386084</v>
       </c>
       <c r="B30" t="n">
         <v>93415</v>
@@ -4052,12 +4060,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4066,10 +4074,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428399</v>
+        <v>428534</v>
       </c>
       <c r="R30" t="n">
-        <v>6799575</v>
+        <v>6799576</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4101,7 +4109,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4111,7 +4119,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4137,13 +4145,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136386090</t>
+          <t>https://artportalen.se/Sighting/136386084</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136392727</v>
+        <v>136386090</v>
       </c>
       <c r="B31" t="n">
         <v>93415</v>
@@ -4187,10 +4195,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428375</v>
+        <v>428399</v>
       </c>
       <c r="R31" t="n">
-        <v>6799813</v>
+        <v>6799575</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4222,7 +4230,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4232,12 +4240,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:44</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska plus fjolårets fruktkroppar.</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4252,24 +4255,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392727</t>
+          <t>https://artportalen.se/Sighting/136386090</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136392735</v>
+        <v>136392727</v>
       </c>
       <c r="B32" t="n">
         <v>93415</v>
@@ -4313,10 +4316,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428420</v>
+        <v>428375</v>
       </c>
       <c r="R32" t="n">
-        <v>6799839</v>
+        <v>6799813</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4348,7 +4351,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4358,7 +4361,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska plus fjolårets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4384,13 +4392,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392735</t>
+          <t>https://artportalen.se/Sighting/136392727</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136392741</v>
+        <v>136392735</v>
       </c>
       <c r="B33" t="n">
         <v>93415</v>
@@ -4420,12 +4428,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4434,13 +4442,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>428462</v>
+        <v>428420</v>
       </c>
       <c r="R33" t="n">
-        <v>6799857</v>
+        <v>6799839</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4469,7 +4477,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4479,7 +4487,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4505,13 +4513,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392741</t>
+          <t>https://artportalen.se/Sighting/136392735</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136392756</v>
+        <v>136392741</v>
       </c>
       <c r="B34" t="n">
         <v>93415</v>
@@ -4541,12 +4549,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4555,13 +4563,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428579</v>
+        <v>428462</v>
       </c>
       <c r="R34" t="n">
-        <v>6799922</v>
+        <v>6799857</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4590,7 +4598,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4600,7 +4608,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4626,13 +4634,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392756</t>
+          <t>https://artportalen.se/Sighting/136392741</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136392771</v>
+        <v>136392756</v>
       </c>
       <c r="B35" t="n">
         <v>93415</v>
@@ -4676,10 +4684,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428738</v>
+        <v>428579</v>
       </c>
       <c r="R35" t="n">
-        <v>6800171</v>
+        <v>6799922</v>
       </c>
       <c r="S35" t="n">
         <v>8</v>
@@ -4711,7 +4719,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4721,7 +4729,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4747,13 +4755,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392771</t>
+          <t>https://artportalen.se/Sighting/136392756</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136392794</v>
+        <v>136392771</v>
       </c>
       <c r="B36" t="n">
         <v>93415</v>
@@ -4797,13 +4805,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428814</v>
+        <v>428738</v>
       </c>
       <c r="R36" t="n">
-        <v>6799909</v>
+        <v>6800171</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4832,7 +4840,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4842,12 +4850,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4873,13 +4876,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392794</t>
+          <t>https://artportalen.se/Sighting/136392771</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136392800</v>
+        <v>136392794</v>
       </c>
       <c r="B37" t="n">
         <v>93415</v>
@@ -4923,13 +4926,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428697</v>
+        <v>428814</v>
       </c>
       <c r="R37" t="n">
-        <v>6799728</v>
+        <v>6799909</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4958,7 +4961,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4968,12 +4971,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>14 fruktkroppar.</t>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4999,13 +5002,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392800</t>
+          <t>https://artportalen.se/Sighting/136392794</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136392803</v>
+        <v>136392800</v>
       </c>
       <c r="B38" t="n">
         <v>93415</v>
@@ -5049,13 +5052,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428686</v>
+        <v>428697</v>
       </c>
       <c r="R38" t="n">
-        <v>6799644</v>
+        <v>6799728</v>
       </c>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5084,7 +5087,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5094,12 +5097,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>14 fruktkroppar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5125,13 +5128,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392803</t>
+          <t>https://artportalen.se/Sighting/136392800</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136392811</v>
+        <v>136392803</v>
       </c>
       <c r="B39" t="n">
         <v>93415</v>
@@ -5169,21 +5172,19 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428523</v>
+        <v>428686</v>
       </c>
       <c r="R39" t="n">
-        <v>6799586</v>
+        <v>6799644</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5212,7 +5213,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5222,7 +5223,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5231,7 +5237,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5243,19 +5248,19 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Anna-Lena Thommson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392811</t>
+          <t>https://artportalen.se/Sighting/136392803</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136392812</v>
+        <v>136392811</v>
       </c>
       <c r="B40" t="n">
         <v>93415</v>
@@ -5301,13 +5306,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428503</v>
+        <v>428523</v>
       </c>
       <c r="R40" t="n">
-        <v>6799568</v>
+        <v>6799586</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5336,7 +5341,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5346,7 +5351,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5373,13 +5378,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392812</t>
+          <t>https://artportalen.se/Sighting/136392811</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136392813</v>
+        <v>136392812</v>
       </c>
       <c r="B41" t="n">
         <v>93415</v>
@@ -5425,13 +5430,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428525</v>
+        <v>428503</v>
       </c>
       <c r="R41" t="n">
-        <v>6799511</v>
+        <v>6799568</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5460,7 +5465,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5470,7 +5475,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5497,13 +5502,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392813</t>
+          <t>https://artportalen.se/Sighting/136392812</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136392823</v>
+        <v>136392813</v>
       </c>
       <c r="B42" t="n">
         <v>93415</v>
@@ -5541,19 +5546,21 @@
           <t>mycel</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428381</v>
+        <v>428525</v>
       </c>
       <c r="R42" t="n">
-        <v>6799586</v>
+        <v>6799511</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5582,7 +5589,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5592,7 +5599,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5601,6 +5608,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5612,19 +5620,19 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392823</t>
+          <t>https://artportalen.se/Sighting/136392813</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136392828</v>
+        <v>136392823</v>
       </c>
       <c r="B43" t="n">
         <v>93415</v>
@@ -5668,13 +5676,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428370</v>
+        <v>428381</v>
       </c>
       <c r="R43" t="n">
-        <v>6799594</v>
+        <v>6799586</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5703,7 +5711,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5713,12 +5721,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar.</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5744,13 +5747,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136392828</t>
+          <t>https://artportalen.se/Sighting/136392823</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136393469</v>
+        <v>136392828</v>
       </c>
       <c r="B44" t="n">
         <v>93415</v>
@@ -5780,29 +5783,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ormtjärn, Dlr</t>
+          <t>Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428264</v>
+        <v>428370</v>
       </c>
       <c r="R44" t="n">
-        <v>6799820</v>
+        <v>6799594</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5831,7 +5832,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5841,7 +5842,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5850,31 +5856,30 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136393469</t>
+          <t>https://artportalen.se/Sighting/136392828</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136396101</v>
+        <v>136393469</v>
       </c>
       <c r="B45" t="n">
         <v>93415</v>
@@ -5904,25 +5909,29 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gryvelån, Dlr</t>
+          <t>Ormtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428325</v>
+        <v>428264</v>
       </c>
       <c r="R45" t="n">
-        <v>6799632</v>
+        <v>6799820</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5951,7 +5960,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5961,7 +5970,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5977,24 +5986,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136396101</t>
+          <t>https://artportalen.se/Sighting/136393469</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136396122</v>
+        <v>136396101</v>
       </c>
       <c r="B46" t="n">
         <v>93415</v>
@@ -6024,7 +6033,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -6036,10 +6045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428619</v>
+        <v>428325</v>
       </c>
       <c r="R46" t="n">
-        <v>6799977</v>
+        <v>6799632</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6071,7 +6080,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6081,12 +6090,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ring 14</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6113,13 +6117,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136396122</t>
+          <t>https://artportalen.se/Sighting/136396101</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136396125</v>
+        <v>136396122</v>
       </c>
       <c r="B47" t="n">
         <v>93415</v>
@@ -6149,7 +6153,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6161,10 +6165,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428654</v>
+        <v>428619</v>
       </c>
       <c r="R47" t="n">
-        <v>6799966</v>
+        <v>6799977</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6196,7 +6200,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6206,12 +6210,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Ring 14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6238,13 +6242,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136396125</t>
+          <t>https://artportalen.se/Sighting/136396122</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136396129</v>
+        <v>136396125</v>
       </c>
       <c r="B48" t="n">
         <v>93415</v>
@@ -6274,7 +6278,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -6286,13 +6290,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428714</v>
+        <v>428654</v>
       </c>
       <c r="R48" t="n">
-        <v>6800083</v>
+        <v>6799966</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6321,7 +6325,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6331,12 +6335,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6363,13 +6367,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136396129</t>
+          <t>https://artportalen.se/Sighting/136396125</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136396130</v>
+        <v>136396129</v>
       </c>
       <c r="B49" t="n">
         <v>93415</v>
@@ -6399,7 +6403,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6411,13 +6415,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428744</v>
+        <v>428714</v>
       </c>
       <c r="R49" t="n">
-        <v>6800092</v>
+        <v>6800083</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6446,7 +6450,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6456,7 +6460,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6488,13 +6492,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136396130</t>
+          <t>https://artportalen.se/Sighting/136396129</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136396135</v>
+        <v>136396130</v>
       </c>
       <c r="B50" t="n">
         <v>93415</v>
@@ -6524,7 +6528,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -6536,13 +6540,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428785</v>
+        <v>428744</v>
       </c>
       <c r="R50" t="n">
-        <v>6800154</v>
+        <v>6800092</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6571,7 +6575,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6581,12 +6585,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6613,13 +6617,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136396135</t>
+          <t>https://artportalen.se/Sighting/136396130</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136396148</v>
+        <v>136396135</v>
       </c>
       <c r="B51" t="n">
         <v>93415</v>
@@ -6647,17 +6651,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gryvelån, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428897</v>
+        <v>428785</v>
       </c>
       <c r="R51" t="n">
-        <v>6800225</v>
+        <v>6800154</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6689,7 +6700,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6699,7 +6710,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6708,6 +6724,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6725,13 +6742,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136396148</t>
+          <t>https://artportalen.se/Sighting/136396135</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136396149</v>
+        <v>136396148</v>
       </c>
       <c r="B52" t="n">
         <v>93415</v>
@@ -6766,10 +6783,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>428900</v>
+        <v>428897</v>
       </c>
       <c r="R52" t="n">
-        <v>6800168</v>
+        <v>6800225</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6801,7 +6818,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6811,12 +6828,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6842,13 +6854,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136396149</t>
+          <t>https://artportalen.se/Sighting/136396148</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136396152</v>
+        <v>136396149</v>
       </c>
       <c r="B53" t="n">
         <v>93415</v>
@@ -6883,10 +6895,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428870</v>
+        <v>428900</v>
       </c>
       <c r="R53" t="n">
-        <v>6800010</v>
+        <v>6800168</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6918,7 +6930,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6928,12 +6940,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6959,13 +6971,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136396152</t>
+          <t>https://artportalen.se/Sighting/136396149</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136396154</v>
+        <v>136396152</v>
       </c>
       <c r="B54" t="n">
         <v>93415</v>
@@ -7000,13 +7012,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428790</v>
+        <v>428870</v>
       </c>
       <c r="R54" t="n">
-        <v>6799972</v>
+        <v>6800010</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7035,7 +7047,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7045,12 +7057,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7076,13 +7088,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136396154</t>
+          <t>https://artportalen.se/Sighting/136396152</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136396155</v>
+        <v>136396154</v>
       </c>
       <c r="B55" t="n">
         <v>93415</v>
@@ -7117,13 +7129,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428773</v>
+        <v>428790</v>
       </c>
       <c r="R55" t="n">
-        <v>6799940</v>
+        <v>6799972</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7152,7 +7164,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7162,12 +7174,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7193,13 +7205,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136396155</t>
+          <t>https://artportalen.se/Sighting/136396154</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136396156</v>
+        <v>136396155</v>
       </c>
       <c r="B56" t="n">
         <v>93415</v>
@@ -7227,24 +7239,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gryvelån, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428787</v>
+        <v>428773</v>
       </c>
       <c r="R56" t="n">
-        <v>6799904</v>
+        <v>6799940</v>
       </c>
       <c r="S56" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7273,7 +7281,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7283,7 +7291,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7292,7 +7305,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7310,16 +7322,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136396156</t>
+          <t>https://artportalen.se/Sighting/136396155</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136402412</v>
+        <v>136396156</v>
       </c>
       <c r="B57" t="n">
-        <v>93416</v>
+        <v>93415</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7344,20 +7356,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gryvlan, Dlr</t>
+          <t>Gryvelån, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>428357</v>
+        <v>428787</v>
       </c>
       <c r="R57" t="n">
-        <v>6799838</v>
+        <v>6799904</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7386,7 +7402,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7396,12 +7412,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:44</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>3 fk.</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7410,30 +7421,31 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136402412</t>
+          <t>https://artportalen.se/Sighting/136396156</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136402421</v>
+        <v>136402412</v>
       </c>
       <c r="B58" t="n">
         <v>93416</v>
@@ -7468,10 +7480,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>428731</v>
+        <v>428357</v>
       </c>
       <c r="R58" t="n">
-        <v>6800176</v>
+        <v>6799838</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7503,7 +7515,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7513,12 +7525,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>2 fk.</t>
+          <t>3 fk.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7544,13 +7556,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136402421</t>
+          <t>https://artportalen.se/Sighting/136402412</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136402428</v>
+        <v>136402421</v>
       </c>
       <c r="B59" t="n">
         <v>93416</v>
@@ -7585,10 +7597,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>428891</v>
+        <v>428731</v>
       </c>
       <c r="R59" t="n">
-        <v>6800113</v>
+        <v>6800176</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7620,7 +7632,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7630,12 +7642,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>1 fk.</t>
+          <t>2 fk.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7661,13 +7673,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136402428</t>
+          <t>https://artportalen.se/Sighting/136402421</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136402429</v>
+        <v>136402428</v>
       </c>
       <c r="B60" t="n">
         <v>93416</v>
@@ -7702,10 +7714,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>428889</v>
+        <v>428891</v>
       </c>
       <c r="R60" t="n">
-        <v>6800093</v>
+        <v>6800113</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7737,7 +7749,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7747,12 +7759,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>10-tal fk.</t>
+          <t>1 fk.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7778,13 +7790,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136402429</t>
+          <t>https://artportalen.se/Sighting/136402428</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136402434</v>
+        <v>136402429</v>
       </c>
       <c r="B61" t="n">
         <v>93416</v>
@@ -7819,10 +7831,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>428867</v>
+        <v>428889</v>
       </c>
       <c r="R61" t="n">
-        <v>6799819</v>
+        <v>6800093</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7854,7 +7866,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7864,12 +7876,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>4 fk.</t>
+          <t>10-tal fk.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7895,13 +7907,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136402434</t>
+          <t>https://artportalen.se/Sighting/136402429</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136402436</v>
+        <v>136402434</v>
       </c>
       <c r="B62" t="n">
         <v>93416</v>
@@ -7936,10 +7948,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>428842</v>
+        <v>428867</v>
       </c>
       <c r="R62" t="n">
-        <v>6799820</v>
+        <v>6799819</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7971,7 +7983,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7981,12 +7993,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>15fk.</t>
+          <t>4 fk.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8012,13 +8024,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136402436</t>
+          <t>https://artportalen.se/Sighting/136402434</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136402438</v>
+        <v>136402436</v>
       </c>
       <c r="B63" t="n">
         <v>93416</v>
@@ -8053,10 +8065,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>428805</v>
+        <v>428842</v>
       </c>
       <c r="R63" t="n">
-        <v>6799788</v>
+        <v>6799820</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8088,7 +8100,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8098,7 +8110,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>15fk.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8124,13 +8141,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136402438</t>
+          <t>https://artportalen.se/Sighting/136402436</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136402439</v>
+        <v>136402438</v>
       </c>
       <c r="B64" t="n">
         <v>93416</v>
@@ -8165,13 +8182,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>428802</v>
+        <v>428805</v>
       </c>
       <c r="R64" t="n">
-        <v>6799789</v>
+        <v>6799788</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8200,7 +8217,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8210,12 +8227,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>3 fk.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8241,13 +8253,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136402439</t>
+          <t>https://artportalen.se/Sighting/136402438</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136402441</v>
+        <v>136402439</v>
       </c>
       <c r="B65" t="n">
         <v>93416</v>
@@ -8282,13 +8294,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>428465</v>
+        <v>428802</v>
       </c>
       <c r="R65" t="n">
-        <v>6799621</v>
+        <v>6799789</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8317,7 +8329,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8327,12 +8339,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>8 fk.</t>
+          <t>3 fk.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8358,13 +8370,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136402441</t>
+          <t>https://artportalen.se/Sighting/136402439</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136402442</v>
+        <v>136402441</v>
       </c>
       <c r="B66" t="n">
         <v>93416</v>
@@ -8399,10 +8411,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>428452</v>
+        <v>428465</v>
       </c>
       <c r="R66" t="n">
-        <v>6799617</v>
+        <v>6799621</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8434,7 +8446,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8444,12 +8456,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>2 fk.</t>
+          <t>8 fk.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8475,13 +8487,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136402442</t>
+          <t>https://artportalen.se/Sighting/136402441</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136405164</v>
+        <v>136402442</v>
       </c>
       <c r="B67" t="n">
         <v>93416</v>
@@ -8509,31 +8521,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storholsrannet, Dlr</t>
+          <t>Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>428605</v>
+        <v>428452</v>
       </c>
       <c r="R67" t="n">
-        <v>6800136</v>
+        <v>6799617</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8560,45 +8561,59 @@
           <t>2026-09-06</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>2 fk.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136405164</t>
+          <t>https://artportalen.se/Sighting/136402442</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136402408</v>
+        <v>136405164</v>
       </c>
       <c r="B68" t="n">
-        <v>93428</v>
+        <v>93416</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8606,37 +8621,48 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gryvlan, Dlr</t>
+          <t>Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>428328</v>
+        <v>428605</v>
       </c>
       <c r="R68" t="n">
-        <v>6799622</v>
+        <v>6800136</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8663,59 +8689,45 @@
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>15-tal fk.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136402408</t>
+          <t>https://artportalen.se/Sighting/136405164</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>137209411</v>
+        <v>136402408</v>
       </c>
       <c r="B69" t="n">
-        <v>93440</v>
+        <v>93428</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8741,22 +8753,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428320</v>
+        <v>428328</v>
       </c>
       <c r="R69" t="n">
-        <v>6799640</v>
+        <v>6799622</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8780,54 +8789,53 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Flera ex, ej räknat. På samma plats där 2 ex av blå taggsvamp noterats tidigare i september i år. Fruktkropparna var nu bruna av ålder, så skicket gör de svåra att säkert arta. Enligt  Björnström/Wikström "Kalkbarrskogens marksvampar" har äldre ex bruna taggar med ljus spets och kan utveckla "lurvig hattyta" och tappa sin blå färg (s 72). Samtidigt kan skarp dropptaggsvamp också se lurvig ut på hatten, så det är kanske det troligaste i detta fall? Inget synligt mycel, om jag minns rätt.</t>
+          <t>15-tal fk.</t>
         </is>
       </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137209411</t>
+          <t>https://artportalen.se/Sighting/136402408</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>137209411</v>
       </c>
       <c r="B19" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>137209411</v>
       </c>
       <c r="B19" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>137209411</v>
       </c>
       <c r="B19" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>137209411</v>
       </c>
       <c r="B19" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>137209411</v>
       </c>
       <c r="B19" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>137209411</v>
       </c>
       <c r="B19" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>137209411</v>
       </c>
       <c r="B19" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>137209411</v>
       </c>
       <c r="B19" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>137209411</v>
       </c>
       <c r="B19" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>137209411</v>
       </c>
       <c r="B19" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>137209411</v>
       </c>
       <c r="B19" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
